--- a/output/index-crime-ytd.xlsx
+++ b/output/index-crime-ytd.xlsx
@@ -913,7 +913,7 @@
         <v>2589</v>
       </c>
       <c r="M2">
-        <v>2382</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>2623</v>
       </c>
       <c r="M3">
-        <v>2599</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>162</v>
       </c>
       <c r="M4">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>2361</v>
       </c>
       <c r="M5">
-        <v>1970</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1047,7 +1047,7 @@
         <v>713</v>
       </c>
       <c r="C6">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D6">
         <v>844</v>
@@ -1074,10 +1074,10 @@
         <v>694</v>
       </c>
       <c r="L6">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="M6">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>156</v>
       </c>
       <c r="M7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>6442</v>
       </c>
       <c r="M8">
-        <v>6911</v>
+        <v>6967</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>2302</v>
       </c>
       <c r="M9">
-        <v>1678</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>22576</v>
       </c>
       <c r="M10">
-        <v>22334</v>
+        <v>22530</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1252,7 +1252,7 @@
         <v>37857</v>
       </c>
       <c r="C11">
-        <v>42145</v>
+        <v>42144</v>
       </c>
       <c r="D11">
         <v>44071</v>
@@ -1279,10 +1279,10 @@
         <v>45322</v>
       </c>
       <c r="L11">
-        <v>39937</v>
+        <v>39939</v>
       </c>
       <c r="M11">
-        <v>38854</v>
+        <v>39175</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1717,7 @@
         <v>245</v>
       </c>
       <c r="M10">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>517</v>
       </c>
       <c r="M11">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +2784,7 @@
         <v>90</v>
       </c>
       <c r="M8">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2866,7 +2866,7 @@
         <v>429</v>
       </c>
       <c r="M10">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2907,7 +2907,7 @@
         <v>654</v>
       </c>
       <c r="M11">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3014,7 @@
         <v>152</v>
       </c>
       <c r="M2">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3055,7 +3055,7 @@
         <v>178</v>
       </c>
       <c r="M3">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3260,7 +3260,7 @@
         <v>296</v>
       </c>
       <c r="M8">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3301,7 +3301,7 @@
         <v>137</v>
       </c>
       <c r="M9">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3342,7 +3342,7 @@
         <v>893</v>
       </c>
       <c r="M10">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3383,7 +3383,7 @@
         <v>1816</v>
       </c>
       <c r="M11">
-        <v>1581</v>
+        <v>1594</v>
       </c>
     </row>
   </sheetData>
@@ -4131,7 +4131,7 @@
         <v>43</v>
       </c>
       <c r="M8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4213,7 +4213,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4254,7 +4254,7 @@
         <v>272</v>
       </c>
       <c r="M11">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4780,7 +4780,7 @@
         <v>63</v>
       </c>
       <c r="M2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4821,7 +4821,7 @@
         <v>85</v>
       </c>
       <c r="M3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4903,7 +4903,7 @@
         <v>46</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5026,7 +5026,7 @@
         <v>152</v>
       </c>
       <c r="M8">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5108,7 +5108,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5149,7 +5149,7 @@
         <v>591</v>
       </c>
       <c r="M11">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -5256,7 +5256,7 @@
         <v>100</v>
       </c>
       <c r="M2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5297,7 +5297,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5338,7 +5338,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5502,7 +5502,7 @@
         <v>173</v>
       </c>
       <c r="M8">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5543,7 +5543,7 @@
         <v>126</v>
       </c>
       <c r="M9">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5584,7 +5584,7 @@
         <v>300</v>
       </c>
       <c r="M10">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5625,7 +5625,7 @@
         <v>894</v>
       </c>
       <c r="M11">
-        <v>952</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -5773,7 +5773,7 @@
         <v>83</v>
       </c>
       <c r="M3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5852,7 +5852,7 @@
         <v>57</v>
       </c>
       <c r="M5">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5975,7 +5975,7 @@
         <v>191</v>
       </c>
       <c r="M8">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6016,7 +6016,7 @@
         <v>46</v>
       </c>
       <c r="M9">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6057,7 +6057,7 @@
         <v>355</v>
       </c>
       <c r="M10">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6098,7 +6098,7 @@
         <v>836</v>
       </c>
       <c r="M11">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -6205,7 +6205,7 @@
         <v>350</v>
       </c>
       <c r="M2">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6287,7 +6287,7 @@
         <v>241</v>
       </c>
       <c r="M4">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6328,7 +6328,7 @@
         <v>106</v>
       </c>
       <c r="M5">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6369,7 +6369,7 @@
         <v>282</v>
       </c>
       <c r="M6">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6410,7 +6410,7 @@
         <v>923</v>
       </c>
       <c r="M7">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6451,7 +6451,7 @@
         <v>1816</v>
       </c>
       <c r="M8">
-        <v>1581</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6492,7 +6492,7 @@
         <v>166</v>
       </c>
       <c r="M9">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6533,7 +6533,7 @@
         <v>428</v>
       </c>
       <c r="M10">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6574,7 +6574,7 @@
         <v>678</v>
       </c>
       <c r="M11">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6615,7 +6615,7 @@
         <v>151</v>
       </c>
       <c r="M12">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6697,7 +6697,7 @@
         <v>261</v>
       </c>
       <c r="M14">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -6738,7 +6738,7 @@
         <v>297</v>
       </c>
       <c r="M15">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6779,7 +6779,7 @@
         <v>281</v>
       </c>
       <c r="M16">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -6861,7 +6861,7 @@
         <v>256</v>
       </c>
       <c r="M18">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -6902,7 +6902,7 @@
         <v>968</v>
       </c>
       <c r="M19">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -6943,7 +6943,7 @@
         <v>710</v>
       </c>
       <c r="M20">
-        <v>653</v>
+        <v>660</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7025,7 +7025,7 @@
         <v>154</v>
       </c>
       <c r="M22">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7066,7 +7066,7 @@
         <v>463</v>
       </c>
       <c r="M23">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7107,7 +7107,7 @@
         <v>191</v>
       </c>
       <c r="M24">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7148,7 +7148,7 @@
         <v>250</v>
       </c>
       <c r="M25">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7189,7 +7189,7 @@
         <v>82</v>
       </c>
       <c r="M26">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7230,7 +7230,7 @@
         <v>536</v>
       </c>
       <c r="M27">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7312,7 +7312,7 @@
         <v>1252</v>
       </c>
       <c r="M29">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7394,7 +7394,7 @@
         <v>368</v>
       </c>
       <c r="M31">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7476,7 +7476,7 @@
         <v>894</v>
       </c>
       <c r="M33">
-        <v>952</v>
+        <v>966</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7517,7 +7517,7 @@
         <v>258</v>
       </c>
       <c r="M34">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7558,7 +7558,7 @@
         <v>123</v>
       </c>
       <c r="M35">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7599,7 +7599,7 @@
         <v>500</v>
       </c>
       <c r="M36">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7640,7 +7640,7 @@
         <v>848</v>
       </c>
       <c r="M37">
-        <v>853</v>
+        <v>861</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -7763,7 +7763,7 @@
         <v>146</v>
       </c>
       <c r="M40">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -7804,7 +7804,7 @@
         <v>141</v>
       </c>
       <c r="M41">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -7845,7 +7845,7 @@
         <v>935</v>
       </c>
       <c r="M42">
-        <v>1106</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -7886,7 +7886,7 @@
         <v>596</v>
       </c>
       <c r="M43">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -7927,7 +7927,7 @@
         <v>370</v>
       </c>
       <c r="M44">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -7968,7 +7968,7 @@
         <v>43</v>
       </c>
       <c r="M45">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -8050,7 +8050,7 @@
         <v>352</v>
       </c>
       <c r="M47">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8091,7 +8091,7 @@
         <v>1023</v>
       </c>
       <c r="M48">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8132,7 +8132,7 @@
         <v>681</v>
       </c>
       <c r="M49">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8173,7 +8173,7 @@
         <v>384</v>
       </c>
       <c r="M50">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8214,7 +8214,7 @@
         <v>563</v>
       </c>
       <c r="M51">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8255,7 +8255,7 @@
         <v>517</v>
       </c>
       <c r="M52">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8296,7 +8296,7 @@
         <v>654</v>
       </c>
       <c r="M53">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8337,7 +8337,7 @@
         <v>1452</v>
       </c>
       <c r="M54">
-        <v>1387</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8378,7 +8378,7 @@
         <v>401</v>
       </c>
       <c r="M55">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8419,7 +8419,7 @@
         <v>195</v>
       </c>
       <c r="M56">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8460,7 +8460,7 @@
         <v>190</v>
       </c>
       <c r="M57">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8542,7 +8542,7 @@
         <v>99</v>
       </c>
       <c r="M59">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8583,7 +8583,7 @@
         <v>272</v>
       </c>
       <c r="M60">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8676,7 +8676,7 @@
         <v>456</v>
       </c>
       <c r="C63">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D63">
         <v>492</v>
@@ -8703,10 +8703,10 @@
         <v>585</v>
       </c>
       <c r="L63">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M63">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -8747,7 +8747,7 @@
         <v>372</v>
       </c>
       <c r="M64">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -8788,7 +8788,7 @@
         <v>532</v>
       </c>
       <c r="M65">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -8829,7 +8829,7 @@
         <v>205</v>
       </c>
       <c r="M66">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -8870,7 +8870,7 @@
         <v>751</v>
       </c>
       <c r="M67">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -8911,7 +8911,7 @@
         <v>219</v>
       </c>
       <c r="M68">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -8993,7 +8993,7 @@
         <v>276</v>
       </c>
       <c r="M70">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9075,7 +9075,7 @@
         <v>265</v>
       </c>
       <c r="M72">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9116,7 +9116,7 @@
         <v>493</v>
       </c>
       <c r="M73">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9157,7 +9157,7 @@
         <v>139</v>
       </c>
       <c r="M74">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9239,7 +9239,7 @@
         <v>1136</v>
       </c>
       <c r="M76">
-        <v>1156</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9280,7 +9280,7 @@
         <v>174</v>
       </c>
       <c r="M77">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9321,7 +9321,7 @@
         <v>634</v>
       </c>
       <c r="M78">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9362,7 +9362,7 @@
         <v>836</v>
       </c>
       <c r="M79">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9444,7 +9444,7 @@
         <v>67</v>
       </c>
       <c r="M81">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -9526,7 +9526,7 @@
         <v>591</v>
       </c>
       <c r="M83">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9567,7 +9567,7 @@
         <v>317</v>
       </c>
       <c r="M84">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9608,7 +9608,7 @@
         <v>1325</v>
       </c>
       <c r="M85">
-        <v>1265</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>314</v>
       </c>
       <c r="M86">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9690,7 +9690,7 @@
         <v>152</v>
       </c>
       <c r="M87">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -9731,7 +9731,7 @@
         <v>329</v>
       </c>
       <c r="M88">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -9772,7 +9772,7 @@
         <v>735</v>
       </c>
       <c r="M89">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -9813,7 +9813,7 @@
         <v>393</v>
       </c>
       <c r="M90">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -9854,7 +9854,7 @@
         <v>371</v>
       </c>
       <c r="M91">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -9895,7 +9895,7 @@
         <v>135</v>
       </c>
       <c r="M92">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -9936,7 +9936,7 @@
         <v>330</v>
       </c>
       <c r="M93">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -9977,7 +9977,7 @@
         <v>951</v>
       </c>
       <c r="M94">
-        <v>1058</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10018,7 +10018,7 @@
         <v>447</v>
       </c>
       <c r="M95">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10059,7 +10059,7 @@
         <v>464</v>
       </c>
       <c r="M96">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10100,7 +10100,7 @@
         <v>681</v>
       </c>
       <c r="M97">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10141,7 +10141,7 @@
         <v>438</v>
       </c>
       <c r="M98">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10182,7 +10182,7 @@
         <v>526</v>
       </c>
       <c r="M99">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10234,7 +10234,7 @@
         <v>37857</v>
       </c>
       <c r="C101">
-        <v>42145</v>
+        <v>42144</v>
       </c>
       <c r="D101">
         <v>44071</v>
@@ -10261,10 +10261,10 @@
         <v>45322</v>
       </c>
       <c r="L101">
-        <v>39937</v>
+        <v>39939</v>
       </c>
       <c r="M101">
-        <v>38854</v>
+        <v>39175</v>
       </c>
     </row>
   </sheetData>
@@ -11163,7 +11163,7 @@
         <v>77</v>
       </c>
       <c r="M10">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11204,7 +11204,7 @@
         <v>146</v>
       </c>
       <c r="M11">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -11597,7 +11597,7 @@
         <v>214</v>
       </c>
       <c r="M10">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11638,7 +11638,7 @@
         <v>372</v>
       </c>
       <c r="M11">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -11868,7 +11868,7 @@
         <v>36</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11909,7 +11909,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11991,7 +11991,7 @@
         <v>103</v>
       </c>
       <c r="M8">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12114,7 +12114,7 @@
         <v>447</v>
       </c>
       <c r="M11">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -12221,7 +12221,7 @@
         <v>90</v>
       </c>
       <c r="M2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12344,7 +12344,7 @@
         <v>46</v>
       </c>
       <c r="M5">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12467,7 +12467,7 @@
         <v>167</v>
       </c>
       <c r="M8">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12508,7 +12508,7 @@
         <v>94</v>
       </c>
       <c r="M9">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -12549,7 +12549,7 @@
         <v>318</v>
       </c>
       <c r="M10">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12590,7 +12590,7 @@
         <v>848</v>
       </c>
       <c r="M11">
-        <v>853</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -12738,7 +12738,7 @@
         <v>49</v>
       </c>
       <c r="M3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12899,7 +12899,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -12940,7 +12940,7 @@
         <v>95</v>
       </c>
       <c r="M8">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13022,7 +13022,7 @@
         <v>248</v>
       </c>
       <c r="M10">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13063,7 +13063,7 @@
         <v>532</v>
       </c>
       <c r="M11">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -13275,7 +13275,7 @@
         <v>48</v>
       </c>
       <c r="M5">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13465,7 +13465,7 @@
         <v>340</v>
       </c>
       <c r="M10">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13506,7 +13506,7 @@
         <v>536</v>
       </c>
       <c r="M11">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -13654,7 +13654,7 @@
         <v>59</v>
       </c>
       <c r="M3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13938,7 +13938,7 @@
         <v>262</v>
       </c>
       <c r="M10">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13979,7 +13979,7 @@
         <v>526</v>
       </c>
       <c r="M11">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -14824,7 +14824,7 @@
         <v>198</v>
       </c>
       <c r="M10">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14865,7 +14865,7 @@
         <v>368</v>
       </c>
       <c r="M11">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -15261,7 +15261,7 @@
         <v>150</v>
       </c>
       <c r="M10">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15302,7 +15302,7 @@
         <v>261</v>
       </c>
       <c r="M11">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -15655,7 +15655,7 @@
         <v>123</v>
       </c>
       <c r="M8">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15737,7 +15737,7 @@
         <v>281</v>
       </c>
       <c r="M10">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15778,7 +15778,7 @@
         <v>751</v>
       </c>
       <c r="M11">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -16189,7 +16189,7 @@
         <v>156</v>
       </c>
       <c r="M10">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16230,7 +16230,7 @@
         <v>317</v>
       </c>
       <c r="M11">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -16439,7 +16439,7 @@
         <v>49</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16544,7 +16544,7 @@
         <v>102</v>
       </c>
       <c r="M8">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16626,7 +16626,7 @@
         <v>697</v>
       </c>
       <c r="M10">
-        <v>758</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16667,7 +16667,7 @@
         <v>951</v>
       </c>
       <c r="M11">
-        <v>1058</v>
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -16885,7 +16885,7 @@
         <v>19</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16993,7 +16993,7 @@
         <v>67</v>
       </c>
       <c r="M8">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17075,7 +17075,7 @@
         <v>941</v>
       </c>
       <c r="M10">
-        <v>921</v>
+        <v>929</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17116,7 +17116,7 @@
         <v>1136</v>
       </c>
       <c r="M11">
-        <v>1156</v>
+        <v>1166</v>
       </c>
     </row>
   </sheetData>
@@ -17485,7 +17485,7 @@
         <v>104</v>
       </c>
       <c r="M10">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17526,7 +17526,7 @@
         <v>152</v>
       </c>
       <c r="M11">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -17741,7 +17741,7 @@
         <v>13</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17937,7 +17937,7 @@
         <v>89</v>
       </c>
       <c r="M10">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17978,7 +17978,7 @@
         <v>250</v>
       </c>
       <c r="M11">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -18651,7 +18651,7 @@
         <v>26</v>
       </c>
       <c r="M8">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18774,7 +18774,7 @@
         <v>281</v>
       </c>
       <c r="M11">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -19082,7 +19082,7 @@
         <v>50</v>
       </c>
       <c r="M8">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19164,7 +19164,7 @@
         <v>530</v>
       </c>
       <c r="M10">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19205,7 +19205,7 @@
         <v>681</v>
       </c>
       <c r="M11">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -19601,7 +19601,7 @@
         <v>447</v>
       </c>
       <c r="M10">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19642,7 +19642,7 @@
         <v>681</v>
       </c>
       <c r="M11">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -19749,7 +19749,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20106,7 +20106,7 @@
         <v>464</v>
       </c>
       <c r="M11">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -20254,7 +20254,7 @@
         <v>26</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20529,7 +20529,7 @@
         <v>224</v>
       </c>
       <c r="M10">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20570,7 +20570,7 @@
         <v>401</v>
       </c>
       <c r="M11">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -20791,7 +20791,7 @@
         <v>38</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20896,7 +20896,7 @@
         <v>120</v>
       </c>
       <c r="M8">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20978,7 +20978,7 @@
         <v>1137</v>
       </c>
       <c r="M10">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21019,7 +21019,7 @@
         <v>1452</v>
       </c>
       <c r="M11">
-        <v>1387</v>
+        <v>1391</v>
       </c>
     </row>
   </sheetData>
@@ -21126,7 +21126,7 @@
         <v>28</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21354,7 +21354,7 @@
         <v>79</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21436,7 +21436,7 @@
         <v>320</v>
       </c>
       <c r="M10">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21477,7 +21477,7 @@
         <v>493</v>
       </c>
       <c r="M11">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -21871,7 +21871,7 @@
         <v>115</v>
       </c>
       <c r="M9">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21912,7 +21912,7 @@
         <v>465</v>
       </c>
       <c r="M10">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21953,7 +21953,7 @@
         <v>1252</v>
       </c>
       <c r="M11">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
   </sheetData>
@@ -22060,7 +22060,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22270,7 +22270,7 @@
         <v>97</v>
       </c>
       <c r="M8">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22352,7 +22352,7 @@
         <v>722</v>
       </c>
       <c r="M10">
-        <v>903</v>
+        <v>909</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22393,7 +22393,7 @@
         <v>1023</v>
       </c>
       <c r="M11">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
   </sheetData>
@@ -22541,7 +22541,7 @@
         <v>70</v>
       </c>
       <c r="M3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22828,7 +22828,7 @@
         <v>511</v>
       </c>
       <c r="M10">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22869,7 +22869,7 @@
         <v>968</v>
       </c>
       <c r="M11">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -22976,7 +22976,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23224,7 +23224,7 @@
         <v>129</v>
       </c>
       <c r="M9">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23265,7 +23265,7 @@
         <v>205</v>
       </c>
       <c r="M10">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -23691,7 +23691,7 @@
         <v>222</v>
       </c>
       <c r="M10">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23732,7 +23732,7 @@
         <v>370</v>
       </c>
       <c r="M11">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -24085,7 +24085,7 @@
         <v>156</v>
       </c>
       <c r="M8">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24167,7 +24167,7 @@
         <v>462</v>
       </c>
       <c r="M10">
-        <v>581</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24208,7 +24208,7 @@
         <v>935</v>
       </c>
       <c r="M11">
-        <v>1106</v>
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
@@ -24589,7 +24589,7 @@
         <v>77</v>
       </c>
       <c r="M10">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24630,7 +24630,7 @@
         <v>154</v>
       </c>
       <c r="M11">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -24778,7 +24778,7 @@
         <v>83</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24819,7 +24819,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24983,7 +24983,7 @@
         <v>219</v>
       </c>
       <c r="M8">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25106,7 +25106,7 @@
         <v>923</v>
       </c>
       <c r="M11">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -25435,7 +25435,7 @@
         <v>78</v>
       </c>
       <c r="M8">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25517,7 +25517,7 @@
         <v>104</v>
       </c>
       <c r="M10">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25558,7 +25558,7 @@
         <v>282</v>
       </c>
       <c r="M11">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -25665,7 +25665,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25963,7 +25963,7 @@
         <v>64</v>
       </c>
       <c r="M10">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26004,7 +26004,7 @@
         <v>141</v>
       </c>
       <c r="M11">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -26424,7 +26424,7 @@
         <v>217</v>
       </c>
       <c r="M10">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26465,7 +26465,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -27075,7 +27075,7 @@
         <v>22</v>
       </c>
       <c r="M5">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27116,7 +27116,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27265,7 +27265,7 @@
         <v>302</v>
       </c>
       <c r="M10">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27306,7 +27306,7 @@
         <v>428</v>
       </c>
       <c r="M11">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -27454,7 +27454,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27547,7 +27547,7 @@
         <v>35</v>
       </c>
       <c r="M6">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27596,7 +27596,7 @@
         <v>25</v>
       </c>
       <c r="M8">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27678,7 +27678,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27719,7 +27719,7 @@
         <v>314</v>
       </c>
       <c r="M11">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -28136,7 +28136,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28177,7 +28177,7 @@
         <v>634</v>
       </c>
       <c r="M11">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -28558,7 +28558,7 @@
         <v>148</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28599,7 +28599,7 @@
         <v>219</v>
       </c>
       <c r="M11">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -28814,7 +28814,7 @@
         <v>17</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28904,7 +28904,7 @@
         <v>37</v>
       </c>
       <c r="M8">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29027,7 +29027,7 @@
         <v>191</v>
       </c>
       <c r="M11">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -29412,7 +29412,7 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29453,7 +29453,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29494,7 +29494,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -29601,7 +29601,7 @@
         <v>52</v>
       </c>
       <c r="M2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29838,7 +29838,7 @@
         <v>83</v>
       </c>
       <c r="M8">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29920,7 +29920,7 @@
         <v>414</v>
       </c>
       <c r="M10">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29961,7 +29961,7 @@
         <v>678</v>
       </c>
       <c r="M11">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -30167,7 +30167,7 @@
         <v>14</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30369,7 +30369,7 @@
         <v>253</v>
       </c>
       <c r="M10">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>463</v>
       </c>
       <c r="M11">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -30517,7 +30517,7 @@
         <v>47</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30754,7 +30754,7 @@
         <v>97</v>
       </c>
       <c r="M8">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30836,7 +30836,7 @@
         <v>139</v>
       </c>
       <c r="M10">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30877,7 +30877,7 @@
         <v>371</v>
       </c>
       <c r="M11">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -31127,7 +31127,7 @@
         <v>15</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -31203,7 +31203,7 @@
         <v>123</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31285,7 +31285,7 @@
         <v>325</v>
       </c>
       <c r="M10">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31326,7 +31326,7 @@
         <v>563</v>
       </c>
       <c r="M11">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -31433,7 +31433,7 @@
         <v>65</v>
       </c>
       <c r="M2">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31556,7 +31556,7 @@
         <v>59</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31679,7 +31679,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31802,7 +31802,7 @@
         <v>710</v>
       </c>
       <c r="M11">
-        <v>653</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -32400,7 +32400,7 @@
         <v>17</v>
       </c>
       <c r="M5">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -32517,7 +32517,7 @@
         <v>71</v>
       </c>
       <c r="M8">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32599,7 +32599,7 @@
         <v>202</v>
       </c>
       <c r="M10">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32640,7 +32640,7 @@
         <v>352</v>
       </c>
       <c r="M11">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -32984,7 +32984,7 @@
         <v>101</v>
       </c>
       <c r="M8">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33107,7 +33107,7 @@
         <v>393</v>
       </c>
       <c r="M11">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -33509,7 +33509,7 @@
         <v>275</v>
       </c>
       <c r="M10">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33550,7 +33550,7 @@
         <v>384</v>
       </c>
       <c r="M11">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -33765,7 +33765,7 @@
         <v>22</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -33949,7 +33949,7 @@
         <v>205</v>
       </c>
       <c r="M10">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33990,7 +33990,7 @@
         <v>330</v>
       </c>
       <c r="M11">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -34097,7 +34097,7 @@
         <v>23</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -34439,7 +34439,7 @@
         <v>256</v>
       </c>
       <c r="M11">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -34799,7 +34799,7 @@
         <v>221</v>
       </c>
       <c r="M10">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34840,7 +34840,7 @@
         <v>276</v>
       </c>
       <c r="M11">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -34947,7 +34947,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35242,7 +35242,7 @@
         <v>72</v>
       </c>
       <c r="M10">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35283,7 +35283,7 @@
         <v>174</v>
       </c>
       <c r="M11">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -35599,7 +35599,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -35640,7 +35640,7 @@
         <v>195</v>
       </c>
       <c r="M10">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -35788,7 +35788,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -36047,7 +36047,7 @@
         <v>106</v>
       </c>
       <c r="M11">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -36379,7 +36379,7 @@
         <v>55</v>
       </c>
       <c r="M8">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36502,7 +36502,7 @@
         <v>350</v>
       </c>
       <c r="M11">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -36798,7 +36798,7 @@
         <v>24</v>
       </c>
       <c r="M8">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36880,7 +36880,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36921,7 +36921,7 @@
         <v>265</v>
       </c>
       <c r="M11">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -37220,7 +37220,7 @@
         <v>59</v>
       </c>
       <c r="M8">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -37302,7 +37302,7 @@
         <v>444</v>
       </c>
       <c r="M10">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37343,7 +37343,7 @@
         <v>596</v>
       </c>
       <c r="M11">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -38158,7 +38158,7 @@
         <v>159</v>
       </c>
       <c r="M10">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38199,7 +38199,7 @@
         <v>241</v>
       </c>
       <c r="M11">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -38347,7 +38347,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -38557,7 +38557,7 @@
         <v>149</v>
       </c>
       <c r="M9">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -38705,7 +38705,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -38933,7 +38933,7 @@
         <v>53</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39015,7 +39015,7 @@
         <v>136</v>
       </c>
       <c r="M10">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39056,7 +39056,7 @@
         <v>258</v>
       </c>
       <c r="M11">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -39163,7 +39163,7 @@
         <v>37</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -39391,7 +39391,7 @@
         <v>52</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39473,7 +39473,7 @@
         <v>518</v>
       </c>
       <c r="M10">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39514,7 +39514,7 @@
         <v>735</v>
       </c>
       <c r="M11">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
   </sheetData>
@@ -39846,7 +39846,7 @@
         <v>97</v>
       </c>
       <c r="M8">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39887,7 +39887,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -40035,7 +40035,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -40265,7 +40265,7 @@
         <v>43</v>
       </c>
       <c r="M10">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -41358,7 +41358,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41399,7 +41399,7 @@
         <v>438</v>
       </c>
       <c r="M11">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -41634,7 +41634,7 @@
         <v>15</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -41716,7 +41716,7 @@
         <v>51</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41757,7 +41757,7 @@
         <v>82</v>
       </c>
       <c r="M9">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -42150,7 +42150,7 @@
         <v>69</v>
       </c>
       <c r="M10">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42191,7 +42191,7 @@
         <v>135</v>
       </c>
       <c r="M11">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -43075,7 +43075,7 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43426,7 +43426,7 @@
         <v>166</v>
       </c>
       <c r="M11">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -43574,7 +43574,7 @@
         <v>173</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43697,7 +43697,7 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -43861,7 +43861,7 @@
         <v>552</v>
       </c>
       <c r="M10">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43902,7 +43902,7 @@
         <v>1325</v>
       </c>
       <c r="M11">
-        <v>1265</v>
+        <v>1277</v>
       </c>
     </row>
   </sheetData>
@@ -44292,7 +44292,7 @@
         <v>60</v>
       </c>
       <c r="M10">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44333,7 +44333,7 @@
         <v>99</v>
       </c>
       <c r="M11">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -45069,7 +45069,7 @@
         <v>118</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45110,7 +45110,7 @@
         <v>190</v>
       </c>
       <c r="M11">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -45536,7 +45536,7 @@
         <v>154</v>
       </c>
       <c r="M10">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45577,7 +45577,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -45905,7 +45905,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45946,7 +45946,7 @@
         <v>139</v>
       </c>
       <c r="M10">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -46632,7 +46632,7 @@
         <v>42</v>
       </c>
       <c r="M10">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46673,7 +46673,7 @@
         <v>67</v>
       </c>
       <c r="M11">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -47360,7 +47360,7 @@
         <v>92</v>
       </c>
       <c r="M10">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47401,7 +47401,7 @@
         <v>151</v>
       </c>
       <c r="M11">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-ytd.xlsx
+++ b/output/index-crime-ytd.xlsx
@@ -913,7 +913,7 @@
         <v>2589</v>
       </c>
       <c r="M2">
-        <v>2399</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>2623</v>
       </c>
       <c r="M3">
-        <v>2617</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>2361</v>
       </c>
       <c r="M5">
-        <v>1987</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1059,7 +1059,7 @@
         <v>796</v>
       </c>
       <c r="G6">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H6">
         <v>672</v>
@@ -1077,7 +1077,7 @@
         <v>728</v>
       </c>
       <c r="M6">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1153,13 +1153,13 @@
         <v>11914</v>
       </c>
       <c r="K8">
-        <v>8879</v>
+        <v>8880</v>
       </c>
       <c r="L8">
-        <v>6442</v>
+        <v>6443</v>
       </c>
       <c r="M8">
-        <v>6967</v>
+        <v>7016</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>2302</v>
       </c>
       <c r="M9">
-        <v>1685</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>22576</v>
       </c>
       <c r="M10">
-        <v>22530</v>
+        <v>22703</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1264,7 +1264,7 @@
         <v>39388</v>
       </c>
       <c r="G11">
-        <v>32523</v>
+        <v>32524</v>
       </c>
       <c r="H11">
         <v>28398</v>
@@ -1276,13 +1276,13 @@
         <v>47029</v>
       </c>
       <c r="K11">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="L11">
-        <v>39939</v>
+        <v>39940</v>
       </c>
       <c r="M11">
-        <v>39175</v>
+        <v>39472</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>54</v>
       </c>
       <c r="M2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>49</v>
       </c>
       <c r="M3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>63</v>
       </c>
       <c r="M8">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>245</v>
       </c>
       <c r="M10">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>517</v>
       </c>
       <c r="M11">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +1971,7 @@
         <v>12</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2012,7 +2012,7 @@
         <v>19</v>
       </c>
       <c r="M8">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2262,7 +2262,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2443,7 +2443,7 @@
         <v>190</v>
       </c>
       <c r="M11">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2550,7 +2550,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2591,7 +2591,7 @@
         <v>25</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2784,7 +2784,7 @@
         <v>90</v>
       </c>
       <c r="M8">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2866,7 +2866,7 @@
         <v>429</v>
       </c>
       <c r="M10">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2907,7 +2907,7 @@
         <v>654</v>
       </c>
       <c r="M11">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3014,7 @@
         <v>152</v>
       </c>
       <c r="M2">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3137,7 +3137,7 @@
         <v>88</v>
       </c>
       <c r="M5">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3178,7 +3178,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3260,7 +3260,7 @@
         <v>296</v>
       </c>
       <c r="M8">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3301,7 +3301,7 @@
         <v>137</v>
       </c>
       <c r="M9">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3342,7 +3342,7 @@
         <v>893</v>
       </c>
       <c r="M10">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3383,7 +3383,7 @@
         <v>1816</v>
       </c>
       <c r="M11">
-        <v>1594</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -3589,7 +3589,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3764,7 +3764,7 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3805,7 +3805,7 @@
         <v>123</v>
       </c>
       <c r="M11">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4213,7 +4213,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4254,7 +4254,7 @@
         <v>272</v>
       </c>
       <c r="M11">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -5026,7 +5026,7 @@
         <v>152</v>
       </c>
       <c r="M8">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5108,7 +5108,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5149,7 +5149,7 @@
         <v>591</v>
       </c>
       <c r="M11">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -5256,7 +5256,7 @@
         <v>100</v>
       </c>
       <c r="M2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5297,7 +5297,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5379,7 +5379,7 @@
         <v>48</v>
       </c>
       <c r="M5">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5502,7 +5502,7 @@
         <v>173</v>
       </c>
       <c r="M8">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5625,7 +5625,7 @@
         <v>894</v>
       </c>
       <c r="M11">
-        <v>966</v>
+        <v>973</v>
       </c>
     </row>
   </sheetData>
@@ -5773,7 +5773,7 @@
         <v>83</v>
       </c>
       <c r="M3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5852,7 +5852,7 @@
         <v>57</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5975,7 +5975,7 @@
         <v>191</v>
       </c>
       <c r="M8">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6057,7 +6057,7 @@
         <v>355</v>
       </c>
       <c r="M10">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6098,7 +6098,7 @@
         <v>836</v>
       </c>
       <c r="M11">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -6205,7 +6205,7 @@
         <v>350</v>
       </c>
       <c r="M2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6328,7 +6328,7 @@
         <v>106</v>
       </c>
       <c r="M5">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6369,7 +6369,7 @@
         <v>282</v>
       </c>
       <c r="M6">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6410,7 +6410,7 @@
         <v>923</v>
       </c>
       <c r="M7">
-        <v>810</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6451,7 +6451,7 @@
         <v>1816</v>
       </c>
       <c r="M8">
-        <v>1594</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6492,7 +6492,7 @@
         <v>166</v>
       </c>
       <c r="M9">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6533,7 +6533,7 @@
         <v>428</v>
       </c>
       <c r="M10">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6574,7 +6574,7 @@
         <v>678</v>
       </c>
       <c r="M11">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6615,7 +6615,7 @@
         <v>151</v>
       </c>
       <c r="M12">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6697,7 +6697,7 @@
         <v>261</v>
       </c>
       <c r="M14">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -6738,7 +6738,7 @@
         <v>297</v>
       </c>
       <c r="M15">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6779,7 +6779,7 @@
         <v>281</v>
       </c>
       <c r="M16">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -6820,7 +6820,7 @@
         <v>39</v>
       </c>
       <c r="M17">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -6902,7 +6902,7 @@
         <v>968</v>
       </c>
       <c r="M19">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -6943,7 +6943,7 @@
         <v>710</v>
       </c>
       <c r="M20">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7025,7 +7025,7 @@
         <v>154</v>
       </c>
       <c r="M22">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7066,7 +7066,7 @@
         <v>463</v>
       </c>
       <c r="M23">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7189,7 +7189,7 @@
         <v>82</v>
       </c>
       <c r="M26">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7230,7 +7230,7 @@
         <v>536</v>
       </c>
       <c r="M27">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7312,7 +7312,7 @@
         <v>1252</v>
       </c>
       <c r="M29">
-        <v>1237</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7394,7 +7394,7 @@
         <v>368</v>
       </c>
       <c r="M31">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7476,7 +7476,7 @@
         <v>894</v>
       </c>
       <c r="M33">
-        <v>966</v>
+        <v>973</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7517,7 +7517,7 @@
         <v>258</v>
       </c>
       <c r="M34">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7558,7 +7558,7 @@
         <v>123</v>
       </c>
       <c r="M35">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7599,7 +7599,7 @@
         <v>500</v>
       </c>
       <c r="M36">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7640,7 +7640,7 @@
         <v>848</v>
       </c>
       <c r="M37">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -7722,7 +7722,7 @@
         <v>67</v>
       </c>
       <c r="M39">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -7763,7 +7763,7 @@
         <v>146</v>
       </c>
       <c r="M40">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -7804,7 +7804,7 @@
         <v>141</v>
       </c>
       <c r="M41">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -7845,7 +7845,7 @@
         <v>935</v>
       </c>
       <c r="M42">
-        <v>1128</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -7886,7 +7886,7 @@
         <v>596</v>
       </c>
       <c r="M43">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -7927,7 +7927,7 @@
         <v>370</v>
       </c>
       <c r="M44">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8009,7 +8009,7 @@
         <v>123</v>
       </c>
       <c r="M46">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -8050,7 +8050,7 @@
         <v>352</v>
       </c>
       <c r="M47">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8091,7 +8091,7 @@
         <v>1023</v>
       </c>
       <c r="M48">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8132,7 +8132,7 @@
         <v>681</v>
       </c>
       <c r="M49">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8173,7 +8173,7 @@
         <v>384</v>
       </c>
       <c r="M50">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8214,7 +8214,7 @@
         <v>563</v>
       </c>
       <c r="M51">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8255,7 +8255,7 @@
         <v>517</v>
       </c>
       <c r="M52">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8296,7 +8296,7 @@
         <v>654</v>
       </c>
       <c r="M53">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8337,7 +8337,7 @@
         <v>1452</v>
       </c>
       <c r="M54">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8378,7 +8378,7 @@
         <v>401</v>
       </c>
       <c r="M55">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8419,7 +8419,7 @@
         <v>195</v>
       </c>
       <c r="M56">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8501,7 +8501,7 @@
         <v>30</v>
       </c>
       <c r="M58">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8583,7 +8583,7 @@
         <v>272</v>
       </c>
       <c r="M60">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8665,7 +8665,7 @@
         <v>19</v>
       </c>
       <c r="M62">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -8688,7 +8688,7 @@
         <v>510</v>
       </c>
       <c r="G63">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H63">
         <v>564</v>
@@ -8700,13 +8700,13 @@
         <v>342</v>
       </c>
       <c r="K63">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L63">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M63">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -8747,7 +8747,7 @@
         <v>372</v>
       </c>
       <c r="M64">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -8788,7 +8788,7 @@
         <v>532</v>
       </c>
       <c r="M65">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -8829,7 +8829,7 @@
         <v>205</v>
       </c>
       <c r="M66">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -8870,7 +8870,7 @@
         <v>751</v>
       </c>
       <c r="M67">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -8952,7 +8952,7 @@
         <v>190</v>
       </c>
       <c r="M69">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -8993,7 +8993,7 @@
         <v>276</v>
       </c>
       <c r="M70">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9075,7 +9075,7 @@
         <v>265</v>
       </c>
       <c r="M72">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9116,7 +9116,7 @@
         <v>493</v>
       </c>
       <c r="M73">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9157,7 +9157,7 @@
         <v>139</v>
       </c>
       <c r="M74">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9239,7 +9239,7 @@
         <v>1136</v>
       </c>
       <c r="M76">
-        <v>1166</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9280,7 +9280,7 @@
         <v>174</v>
       </c>
       <c r="M77">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9321,7 +9321,7 @@
         <v>634</v>
       </c>
       <c r="M78">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9362,7 +9362,7 @@
         <v>836</v>
       </c>
       <c r="M79">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9403,7 +9403,7 @@
         <v>187</v>
       </c>
       <c r="M80">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9526,7 +9526,7 @@
         <v>591</v>
       </c>
       <c r="M83">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9567,7 +9567,7 @@
         <v>317</v>
       </c>
       <c r="M84">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9608,7 +9608,7 @@
         <v>1325</v>
       </c>
       <c r="M85">
-        <v>1277</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>314</v>
       </c>
       <c r="M86">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9690,7 +9690,7 @@
         <v>152</v>
       </c>
       <c r="M87">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -9731,7 +9731,7 @@
         <v>329</v>
       </c>
       <c r="M88">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -9772,7 +9772,7 @@
         <v>735</v>
       </c>
       <c r="M89">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -9813,7 +9813,7 @@
         <v>393</v>
       </c>
       <c r="M90">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -9854,7 +9854,7 @@
         <v>371</v>
       </c>
       <c r="M91">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -9936,7 +9936,7 @@
         <v>330</v>
       </c>
       <c r="M93">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -9977,7 +9977,7 @@
         <v>951</v>
       </c>
       <c r="M94">
-        <v>1073</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10018,7 +10018,7 @@
         <v>447</v>
       </c>
       <c r="M95">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10059,7 +10059,7 @@
         <v>464</v>
       </c>
       <c r="M96">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10100,7 +10100,7 @@
         <v>681</v>
       </c>
       <c r="M97">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10141,7 +10141,7 @@
         <v>438</v>
       </c>
       <c r="M98">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10182,7 +10182,7 @@
         <v>526</v>
       </c>
       <c r="M99">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10246,7 +10246,7 @@
         <v>39388</v>
       </c>
       <c r="G101">
-        <v>32523</v>
+        <v>32524</v>
       </c>
       <c r="H101">
         <v>28398</v>
@@ -10258,13 +10258,13 @@
         <v>47029</v>
       </c>
       <c r="K101">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="L101">
-        <v>39939</v>
+        <v>39940</v>
       </c>
       <c r="M101">
-        <v>39175</v>
+        <v>39472</v>
       </c>
     </row>
   </sheetData>
@@ -11163,7 +11163,7 @@
         <v>77</v>
       </c>
       <c r="M10">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11204,7 +11204,7 @@
         <v>146</v>
       </c>
       <c r="M11">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -11515,7 +11515,7 @@
         <v>84</v>
       </c>
       <c r="M8">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11597,7 +11597,7 @@
         <v>214</v>
       </c>
       <c r="M10">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11638,7 +11638,7 @@
         <v>372</v>
       </c>
       <c r="M11">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -11868,7 +11868,7 @@
         <v>36</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12073,7 +12073,7 @@
         <v>185</v>
       </c>
       <c r="M10">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12114,7 +12114,7 @@
         <v>447</v>
       </c>
       <c r="M11">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -12221,7 +12221,7 @@
         <v>90</v>
       </c>
       <c r="M2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12385,7 +12385,7 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12467,7 +12467,7 @@
         <v>167</v>
       </c>
       <c r="M8">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12508,7 +12508,7 @@
         <v>94</v>
       </c>
       <c r="M9">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -12590,7 +12590,7 @@
         <v>848</v>
       </c>
       <c r="M11">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -12697,7 +12697,7 @@
         <v>57</v>
       </c>
       <c r="M2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12738,7 +12738,7 @@
         <v>49</v>
       </c>
       <c r="M3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12820,7 +12820,7 @@
         <v>28</v>
       </c>
       <c r="M5">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12861,7 +12861,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12940,7 +12940,7 @@
         <v>95</v>
       </c>
       <c r="M8">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13063,7 +13063,7 @@
         <v>532</v>
       </c>
       <c r="M11">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -13316,7 +13316,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13465,7 +13465,7 @@
         <v>340</v>
       </c>
       <c r="M10">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13506,7 +13506,7 @@
         <v>536</v>
       </c>
       <c r="M11">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -13654,7 +13654,7 @@
         <v>59</v>
       </c>
       <c r="M3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13733,7 +13733,7 @@
         <v>33</v>
       </c>
       <c r="M5">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13856,7 +13856,7 @@
         <v>93</v>
       </c>
       <c r="M8">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13938,7 +13938,7 @@
         <v>262</v>
       </c>
       <c r="M10">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13979,7 +13979,7 @@
         <v>526</v>
       </c>
       <c r="M11">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -14505,7 +14505,7 @@
         <v>28</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14824,7 +14824,7 @@
         <v>198</v>
       </c>
       <c r="M10">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14865,7 +14865,7 @@
         <v>368</v>
       </c>
       <c r="M11">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -15071,7 +15071,7 @@
         <v>25</v>
       </c>
       <c r="M5">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15261,7 +15261,7 @@
         <v>150</v>
       </c>
       <c r="M10">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15302,7 +15302,7 @@
         <v>261</v>
       </c>
       <c r="M11">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -15573,7 +15573,7 @@
         <v>27</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15737,7 +15737,7 @@
         <v>281</v>
       </c>
       <c r="M10">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15778,7 +15778,7 @@
         <v>751</v>
       </c>
       <c r="M11">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -15885,7 +15885,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16189,7 +16189,7 @@
         <v>156</v>
       </c>
       <c r="M10">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16230,7 +16230,7 @@
         <v>317</v>
       </c>
       <c r="M11">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -16544,7 +16544,7 @@
         <v>102</v>
       </c>
       <c r="M8">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16626,7 +16626,7 @@
         <v>697</v>
       </c>
       <c r="M10">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16667,7 +16667,7 @@
         <v>951</v>
       </c>
       <c r="M11">
-        <v>1073</v>
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
@@ -16993,7 +16993,7 @@
         <v>67</v>
       </c>
       <c r="M8">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17075,7 +17075,7 @@
         <v>941</v>
       </c>
       <c r="M10">
-        <v>929</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17116,7 +17116,7 @@
         <v>1136</v>
       </c>
       <c r="M11">
-        <v>1166</v>
+        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -17485,7 +17485,7 @@
         <v>104</v>
       </c>
       <c r="M10">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17526,7 +17526,7 @@
         <v>152</v>
       </c>
       <c r="M11">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -18651,7 +18651,7 @@
         <v>26</v>
       </c>
       <c r="M8">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18733,7 +18733,7 @@
         <v>215</v>
       </c>
       <c r="M10">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18774,7 +18774,7 @@
         <v>281</v>
       </c>
       <c r="M11">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -18922,7 +18922,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19082,7 +19082,7 @@
         <v>50</v>
       </c>
       <c r="M8">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19164,7 +19164,7 @@
         <v>530</v>
       </c>
       <c r="M10">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19205,7 +19205,7 @@
         <v>681</v>
       </c>
       <c r="M11">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -19519,7 +19519,7 @@
         <v>114</v>
       </c>
       <c r="M8">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19601,7 +19601,7 @@
         <v>447</v>
       </c>
       <c r="M10">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19642,7 +19642,7 @@
         <v>681</v>
       </c>
       <c r="M11">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -20065,7 +20065,7 @@
         <v>259</v>
       </c>
       <c r="M10">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20106,7 +20106,7 @@
         <v>464</v>
       </c>
       <c r="M11">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -20529,7 +20529,7 @@
         <v>224</v>
       </c>
       <c r="M10">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20570,7 +20570,7 @@
         <v>401</v>
       </c>
       <c r="M11">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -20978,7 +20978,7 @@
         <v>1137</v>
       </c>
       <c r="M10">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21019,7 +21019,7 @@
         <v>1452</v>
       </c>
       <c r="M11">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
   </sheetData>
@@ -21126,7 +21126,7 @@
         <v>28</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21354,7 +21354,7 @@
         <v>79</v>
       </c>
       <c r="M8">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21436,7 +21436,7 @@
         <v>320</v>
       </c>
       <c r="M10">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21477,7 +21477,7 @@
         <v>493</v>
       </c>
       <c r="M11">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -21584,7 +21584,7 @@
         <v>141</v>
       </c>
       <c r="M2">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21625,7 +21625,7 @@
         <v>161</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21707,7 +21707,7 @@
         <v>81</v>
       </c>
       <c r="M5">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21830,7 +21830,7 @@
         <v>252</v>
       </c>
       <c r="M8">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21953,7 +21953,7 @@
         <v>1252</v>
       </c>
       <c r="M11">
-        <v>1237</v>
+        <v>1244</v>
       </c>
     </row>
   </sheetData>
@@ -22168,7 +22168,7 @@
         <v>87</v>
       </c>
       <c r="M5">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22270,7 +22270,7 @@
         <v>97</v>
       </c>
       <c r="M8">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22352,7 +22352,7 @@
         <v>722</v>
       </c>
       <c r="M10">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22393,7 +22393,7 @@
         <v>1023</v>
       </c>
       <c r="M11">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
   </sheetData>
@@ -22746,7 +22746,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22787,7 +22787,7 @@
         <v>73</v>
       </c>
       <c r="M9">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -22828,7 +22828,7 @@
         <v>511</v>
       </c>
       <c r="M10">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22869,7 +22869,7 @@
         <v>968</v>
       </c>
       <c r="M11">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -23142,7 +23142,7 @@
         <v>30</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -23265,7 +23265,7 @@
         <v>205</v>
       </c>
       <c r="M10">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -23609,7 +23609,7 @@
         <v>62</v>
       </c>
       <c r="M8">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23691,7 +23691,7 @@
         <v>222</v>
       </c>
       <c r="M10">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23732,7 +23732,7 @@
         <v>370</v>
       </c>
       <c r="M11">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -23880,7 +23880,7 @@
         <v>86</v>
       </c>
       <c r="M3">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23962,7 +23962,7 @@
         <v>47</v>
       </c>
       <c r="M5">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24085,7 +24085,7 @@
         <v>156</v>
       </c>
       <c r="M8">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24167,7 +24167,7 @@
         <v>462</v>
       </c>
       <c r="M10">
-        <v>597</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24208,7 +24208,7 @@
         <v>935</v>
       </c>
       <c r="M11">
-        <v>1128</v>
+        <v>1148</v>
       </c>
     </row>
   </sheetData>
@@ -24510,7 +24510,7 @@
         <v>37</v>
       </c>
       <c r="M8">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24589,7 +24589,7 @@
         <v>77</v>
       </c>
       <c r="M10">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24630,7 +24630,7 @@
         <v>154</v>
       </c>
       <c r="M11">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -24860,7 +24860,7 @@
         <v>66</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24983,7 +24983,7 @@
         <v>219</v>
       </c>
       <c r="M8">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25065,7 +25065,7 @@
         <v>362</v>
       </c>
       <c r="M10">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25106,7 +25106,7 @@
         <v>923</v>
       </c>
       <c r="M11">
-        <v>810</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -25517,7 +25517,7 @@
         <v>104</v>
       </c>
       <c r="M10">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25558,7 +25558,7 @@
         <v>282</v>
       </c>
       <c r="M11">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -25706,7 +25706,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25779,7 +25779,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -26004,7 +26004,7 @@
         <v>141</v>
       </c>
       <c r="M11">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -26342,7 +26342,7 @@
         <v>150</v>
       </c>
       <c r="M8">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26383,7 +26383,7 @@
         <v>25</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -26465,7 +26465,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -27265,7 +27265,7 @@
         <v>302</v>
       </c>
       <c r="M10">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27306,7 +27306,7 @@
         <v>428</v>
       </c>
       <c r="M11">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -27678,7 +27678,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27719,7 +27719,7 @@
         <v>314</v>
       </c>
       <c r="M11">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -28054,7 +28054,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28136,7 +28136,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28177,7 +28177,7 @@
         <v>634</v>
       </c>
       <c r="M11">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -29295,7 +29295,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -29494,7 +29494,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -29721,7 +29721,7 @@
         <v>38</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29920,7 +29920,7 @@
         <v>414</v>
       </c>
       <c r="M10">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29961,7 +29961,7 @@
         <v>678</v>
       </c>
       <c r="M11">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -30208,7 +30208,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -30369,7 +30369,7 @@
         <v>253</v>
       </c>
       <c r="M10">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>463</v>
       </c>
       <c r="M11">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -30558,7 +30558,7 @@
         <v>43</v>
       </c>
       <c r="M3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30634,7 +30634,7 @@
         <v>15</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30836,7 +30836,7 @@
         <v>139</v>
       </c>
       <c r="M10">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30877,7 +30877,7 @@
         <v>371</v>
       </c>
       <c r="M11">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -31086,7 +31086,7 @@
         <v>18</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31285,7 +31285,7 @@
         <v>325</v>
       </c>
       <c r="M10">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31326,7 +31326,7 @@
         <v>563</v>
       </c>
       <c r="M11">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -31433,7 +31433,7 @@
         <v>65</v>
       </c>
       <c r="M2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31474,7 +31474,7 @@
         <v>66</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31720,7 +31720,7 @@
         <v>59</v>
       </c>
       <c r="M9">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -31761,7 +31761,7 @@
         <v>334</v>
       </c>
       <c r="M10">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31802,7 +31802,7 @@
         <v>710</v>
       </c>
       <c r="M11">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -32599,7 +32599,7 @@
         <v>202</v>
       </c>
       <c r="M10">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32640,7 +32640,7 @@
         <v>352</v>
       </c>
       <c r="M11">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -33066,7 +33066,7 @@
         <v>182</v>
       </c>
       <c r="M10">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33107,7 +33107,7 @@
         <v>393</v>
       </c>
       <c r="M11">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -33509,7 +33509,7 @@
         <v>275</v>
       </c>
       <c r="M10">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33550,7 +33550,7 @@
         <v>384</v>
       </c>
       <c r="M11">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -33908,7 +33908,7 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -33949,7 +33949,7 @@
         <v>205</v>
       </c>
       <c r="M10">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33990,7 +33990,7 @@
         <v>330</v>
       </c>
       <c r="M11">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -34799,7 +34799,7 @@
         <v>221</v>
       </c>
       <c r="M10">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34840,7 +34840,7 @@
         <v>276</v>
       </c>
       <c r="M11">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -34988,7 +34988,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35283,7 +35283,7 @@
         <v>174</v>
       </c>
       <c r="M11">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -35458,6 +35458,9 @@
       <c r="K5">
         <v>4</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -35599,7 +35602,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -35640,7 +35643,7 @@
         <v>195</v>
       </c>
       <c r="M10">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -36006,7 +36009,7 @@
         <v>49</v>
       </c>
       <c r="M10">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36047,7 +36050,7 @@
         <v>106</v>
       </c>
       <c r="M11">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -36262,7 +36265,7 @@
         <v>15</v>
       </c>
       <c r="M5">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -36461,7 +36464,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36502,7 +36505,7 @@
         <v>350</v>
       </c>
       <c r="M11">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -36798,7 +36801,7 @@
         <v>24</v>
       </c>
       <c r="M8">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36880,7 +36883,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36921,7 +36924,7 @@
         <v>265</v>
       </c>
       <c r="M11">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -37028,7 +37031,7 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -37168,7 +37171,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -37220,7 +37223,7 @@
         <v>59</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -37302,7 +37305,7 @@
         <v>444</v>
       </c>
       <c r="M10">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37343,7 +37346,7 @@
         <v>596</v>
       </c>
       <c r="M11">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -37642,7 +37645,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -37765,7 +37768,7 @@
         <v>39</v>
       </c>
       <c r="M11">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -38557,7 +38560,7 @@
         <v>149</v>
       </c>
       <c r="M9">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -38598,7 +38601,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -39015,7 +39018,7 @@
         <v>136</v>
       </c>
       <c r="M10">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39056,7 +39059,7 @@
         <v>258</v>
       </c>
       <c r="M11">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -39432,7 +39435,7 @@
         <v>27</v>
       </c>
       <c r="M9">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -39473,7 +39476,7 @@
         <v>518</v>
       </c>
       <c r="M10">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39514,7 +39517,7 @@
         <v>735</v>
       </c>
       <c r="M11">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -39846,7 +39849,7 @@
         <v>97</v>
       </c>
       <c r="M8">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39887,7 +39890,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -40942,7 +40945,7 @@
         <v>25</v>
       </c>
       <c r="M10">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40983,7 +40986,7 @@
         <v>30</v>
       </c>
       <c r="M11">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -41276,7 +41279,7 @@
         <v>64</v>
       </c>
       <c r="M8">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41358,7 +41361,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41399,7 +41402,7 @@
         <v>438</v>
       </c>
       <c r="M11">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -41716,7 +41719,7 @@
         <v>51</v>
       </c>
       <c r="M8">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41757,7 +41760,7 @@
         <v>82</v>
       </c>
       <c r="M9">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -43303,7 +43306,7 @@
         <v>41</v>
       </c>
       <c r="M8">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43426,7 +43429,7 @@
         <v>166</v>
       </c>
       <c r="M11">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -43574,7 +43577,7 @@
         <v>173</v>
       </c>
       <c r="M3">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43656,7 +43659,7 @@
         <v>106</v>
       </c>
       <c r="M5">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43820,7 +43823,7 @@
         <v>85</v>
       </c>
       <c r="M9">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43861,7 +43864,7 @@
         <v>552</v>
       </c>
       <c r="M10">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43902,7 +43905,7 @@
         <v>1325</v>
       </c>
       <c r="M11">
-        <v>1277</v>
+        <v>1289</v>
       </c>
     </row>
   </sheetData>
@@ -44635,7 +44638,7 @@
         <v>56</v>
       </c>
       <c r="M8">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44676,7 +44679,7 @@
         <v>67</v>
       </c>
       <c r="M9">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -45536,7 +45539,7 @@
         <v>154</v>
       </c>
       <c r="M10">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45577,7 +45580,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -45905,7 +45908,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45946,7 +45949,7 @@
         <v>139</v>
       </c>
       <c r="M10">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -47278,7 +47281,7 @@
         <v>26</v>
       </c>
       <c r="M8">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47401,7 +47404,7 @@
         <v>151</v>
       </c>
       <c r="M11">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-ytd.xlsx
+++ b/output/index-crime-ytd.xlsx
@@ -913,7 +913,7 @@
         <v>2589</v>
       </c>
       <c r="M2">
-        <v>2415</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>2623</v>
       </c>
       <c r="M3">
-        <v>2637</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>162</v>
       </c>
       <c r="M4">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>2361</v>
       </c>
       <c r="M5">
-        <v>2013</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>728</v>
       </c>
       <c r="M6">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>156</v>
       </c>
       <c r="M7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>6443</v>
       </c>
       <c r="M8">
-        <v>7016</v>
+        <v>7071</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>2302</v>
       </c>
       <c r="M9">
-        <v>1695</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>22576</v>
       </c>
       <c r="M10">
-        <v>22703</v>
+        <v>22877</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1282,7 +1282,7 @@
         <v>39940</v>
       </c>
       <c r="M11">
-        <v>39472</v>
+        <v>39766</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>54</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1512,7 +1512,7 @@
         <v>42</v>
       </c>
       <c r="M5">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>517</v>
       </c>
       <c r="M11">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -2402,7 +2402,7 @@
         <v>135</v>
       </c>
       <c r="M10">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2443,7 +2443,7 @@
         <v>190</v>
       </c>
       <c r="M11">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +2866,7 @@
         <v>429</v>
       </c>
       <c r="M10">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2907,7 +2907,7 @@
         <v>654</v>
       </c>
       <c r="M11">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3014,7 @@
         <v>152</v>
       </c>
       <c r="M2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3260,7 +3260,7 @@
         <v>296</v>
       </c>
       <c r="M8">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3342,7 +3342,7 @@
         <v>893</v>
       </c>
       <c r="M10">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3383,7 +3383,7 @@
         <v>1816</v>
       </c>
       <c r="M11">
-        <v>1605</v>
+        <v>1616</v>
       </c>
     </row>
   </sheetData>
@@ -4213,7 +4213,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4254,7 +4254,7 @@
         <v>272</v>
       </c>
       <c r="M11">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -4550,7 +4550,7 @@
         <v>46</v>
       </c>
       <c r="M8">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4673,7 +4673,7 @@
         <v>128</v>
       </c>
       <c r="M11">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -4821,7 +4821,7 @@
         <v>85</v>
       </c>
       <c r="M3">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4985,7 +4985,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5026,7 +5026,7 @@
         <v>152</v>
       </c>
       <c r="M8">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5108,7 +5108,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5149,7 +5149,7 @@
         <v>591</v>
       </c>
       <c r="M11">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -5297,7 +5297,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5379,7 +5379,7 @@
         <v>48</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5420,7 +5420,7 @@
         <v>22</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5502,7 +5502,7 @@
         <v>173</v>
       </c>
       <c r="M8">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5584,7 +5584,7 @@
         <v>300</v>
       </c>
       <c r="M10">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5625,7 +5625,7 @@
         <v>894</v>
       </c>
       <c r="M11">
-        <v>973</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>
@@ -5975,7 +5975,7 @@
         <v>191</v>
       </c>
       <c r="M8">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6057,7 +6057,7 @@
         <v>355</v>
       </c>
       <c r="M10">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6098,7 +6098,7 @@
         <v>836</v>
       </c>
       <c r="M11">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -6205,7 +6205,7 @@
         <v>350</v>
       </c>
       <c r="M2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6287,7 +6287,7 @@
         <v>241</v>
       </c>
       <c r="M4">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6328,7 +6328,7 @@
         <v>106</v>
       </c>
       <c r="M5">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6369,7 +6369,7 @@
         <v>282</v>
       </c>
       <c r="M6">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6410,7 +6410,7 @@
         <v>923</v>
       </c>
       <c r="M7">
-        <v>814</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6451,7 +6451,7 @@
         <v>1816</v>
       </c>
       <c r="M8">
-        <v>1605</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6533,7 +6533,7 @@
         <v>428</v>
       </c>
       <c r="M10">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6574,7 +6574,7 @@
         <v>678</v>
       </c>
       <c r="M11">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6615,7 +6615,7 @@
         <v>151</v>
       </c>
       <c r="M12">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6697,7 +6697,7 @@
         <v>261</v>
       </c>
       <c r="M14">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -6738,7 +6738,7 @@
         <v>297</v>
       </c>
       <c r="M15">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6861,7 +6861,7 @@
         <v>256</v>
       </c>
       <c r="M18">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -6902,7 +6902,7 @@
         <v>968</v>
       </c>
       <c r="M19">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -6943,7 +6943,7 @@
         <v>710</v>
       </c>
       <c r="M20">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7066,7 +7066,7 @@
         <v>463</v>
       </c>
       <c r="M23">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7107,7 +7107,7 @@
         <v>191</v>
       </c>
       <c r="M24">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7148,7 +7148,7 @@
         <v>250</v>
       </c>
       <c r="M25">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7189,7 +7189,7 @@
         <v>82</v>
       </c>
       <c r="M26">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7230,7 +7230,7 @@
         <v>536</v>
       </c>
       <c r="M27">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7271,7 +7271,7 @@
         <v>43</v>
       </c>
       <c r="M28">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -7312,7 +7312,7 @@
         <v>1252</v>
       </c>
       <c r="M29">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7353,7 +7353,7 @@
         <v>99</v>
       </c>
       <c r="M30">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7394,7 +7394,7 @@
         <v>368</v>
       </c>
       <c r="M31">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7476,7 +7476,7 @@
         <v>894</v>
       </c>
       <c r="M33">
-        <v>973</v>
+        <v>980</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7517,7 +7517,7 @@
         <v>258</v>
       </c>
       <c r="M34">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7599,7 +7599,7 @@
         <v>500</v>
       </c>
       <c r="M36">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7640,7 +7640,7 @@
         <v>848</v>
       </c>
       <c r="M37">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -7722,7 +7722,7 @@
         <v>67</v>
       </c>
       <c r="M39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -7763,7 +7763,7 @@
         <v>146</v>
       </c>
       <c r="M40">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -7804,7 +7804,7 @@
         <v>141</v>
       </c>
       <c r="M41">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -7845,7 +7845,7 @@
         <v>935</v>
       </c>
       <c r="M42">
-        <v>1148</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -7886,7 +7886,7 @@
         <v>596</v>
       </c>
       <c r="M43">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -7927,7 +7927,7 @@
         <v>370</v>
       </c>
       <c r="M44">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8050,7 +8050,7 @@
         <v>352</v>
       </c>
       <c r="M47">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8091,7 +8091,7 @@
         <v>1023</v>
       </c>
       <c r="M48">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8132,7 +8132,7 @@
         <v>681</v>
       </c>
       <c r="M49">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8173,7 +8173,7 @@
         <v>384</v>
       </c>
       <c r="M50">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8214,7 +8214,7 @@
         <v>563</v>
       </c>
       <c r="M51">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8255,7 +8255,7 @@
         <v>517</v>
       </c>
       <c r="M52">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8296,7 +8296,7 @@
         <v>654</v>
       </c>
       <c r="M53">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8337,7 +8337,7 @@
         <v>1452</v>
       </c>
       <c r="M54">
-        <v>1393</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8419,7 +8419,7 @@
         <v>195</v>
       </c>
       <c r="M56">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8501,7 +8501,7 @@
         <v>30</v>
       </c>
       <c r="M58">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8542,7 +8542,7 @@
         <v>99</v>
       </c>
       <c r="M59">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8583,7 +8583,7 @@
         <v>272</v>
       </c>
       <c r="M60">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8706,7 +8706,7 @@
         <v>719</v>
       </c>
       <c r="M63">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -8747,7 +8747,7 @@
         <v>372</v>
       </c>
       <c r="M64">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -8788,7 +8788,7 @@
         <v>532</v>
       </c>
       <c r="M65">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -8829,7 +8829,7 @@
         <v>205</v>
       </c>
       <c r="M66">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -8870,7 +8870,7 @@
         <v>751</v>
       </c>
       <c r="M67">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -8911,7 +8911,7 @@
         <v>219</v>
       </c>
       <c r="M68">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -8952,7 +8952,7 @@
         <v>190</v>
       </c>
       <c r="M69">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -8993,7 +8993,7 @@
         <v>276</v>
       </c>
       <c r="M70">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9034,7 +9034,7 @@
         <v>128</v>
       </c>
       <c r="M71">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9075,7 +9075,7 @@
         <v>265</v>
       </c>
       <c r="M72">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9116,7 +9116,7 @@
         <v>493</v>
       </c>
       <c r="M73">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9157,7 +9157,7 @@
         <v>139</v>
       </c>
       <c r="M74">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9198,7 +9198,7 @@
         <v>197</v>
       </c>
       <c r="M75">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9239,7 +9239,7 @@
         <v>1136</v>
       </c>
       <c r="M76">
-        <v>1178</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9321,7 +9321,7 @@
         <v>634</v>
       </c>
       <c r="M78">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9362,7 +9362,7 @@
         <v>836</v>
       </c>
       <c r="M79">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9403,7 +9403,7 @@
         <v>187</v>
       </c>
       <c r="M80">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9444,7 +9444,7 @@
         <v>67</v>
       </c>
       <c r="M81">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -9485,7 +9485,7 @@
         <v>103</v>
       </c>
       <c r="M82">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -9526,7 +9526,7 @@
         <v>591</v>
       </c>
       <c r="M83">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9567,7 +9567,7 @@
         <v>317</v>
       </c>
       <c r="M84">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9608,7 +9608,7 @@
         <v>1325</v>
       </c>
       <c r="M85">
-        <v>1289</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9649,7 +9649,7 @@
         <v>314</v>
       </c>
       <c r="M86">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9731,7 +9731,7 @@
         <v>329</v>
       </c>
       <c r="M88">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -9772,7 +9772,7 @@
         <v>735</v>
       </c>
       <c r="M89">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -9813,7 +9813,7 @@
         <v>393</v>
       </c>
       <c r="M90">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -9854,7 +9854,7 @@
         <v>371</v>
       </c>
       <c r="M91">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -9936,7 +9936,7 @@
         <v>330</v>
       </c>
       <c r="M93">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -9977,7 +9977,7 @@
         <v>951</v>
       </c>
       <c r="M94">
-        <v>1080</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10018,7 +10018,7 @@
         <v>447</v>
       </c>
       <c r="M95">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10059,7 +10059,7 @@
         <v>464</v>
       </c>
       <c r="M96">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10100,7 +10100,7 @@
         <v>681</v>
       </c>
       <c r="M97">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10141,7 +10141,7 @@
         <v>438</v>
       </c>
       <c r="M98">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10182,7 +10182,7 @@
         <v>526</v>
       </c>
       <c r="M99">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10264,7 +10264,7 @@
         <v>39940</v>
       </c>
       <c r="M101">
-        <v>39472</v>
+        <v>39766</v>
       </c>
     </row>
   </sheetData>
@@ -10662,7 +10662,7 @@
         <v>34</v>
       </c>
       <c r="M8">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -10744,7 +10744,7 @@
         <v>124</v>
       </c>
       <c r="M10">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -10785,7 +10785,7 @@
         <v>197</v>
       </c>
       <c r="M11">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -11163,7 +11163,7 @@
         <v>77</v>
       </c>
       <c r="M10">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11204,7 +11204,7 @@
         <v>146</v>
       </c>
       <c r="M11">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -11404,7 +11404,7 @@
         <v>20</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11515,7 +11515,7 @@
         <v>84</v>
       </c>
       <c r="M8">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11597,7 +11597,7 @@
         <v>214</v>
       </c>
       <c r="M10">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11638,7 +11638,7 @@
         <v>372</v>
       </c>
       <c r="M11">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -11868,7 +11868,7 @@
         <v>36</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12114,7 +12114,7 @@
         <v>447</v>
       </c>
       <c r="M11">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -12262,7 +12262,7 @@
         <v>92</v>
       </c>
       <c r="M3">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12467,7 +12467,7 @@
         <v>167</v>
       </c>
       <c r="M8">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12549,7 +12549,7 @@
         <v>318</v>
       </c>
       <c r="M10">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12590,7 +12590,7 @@
         <v>848</v>
       </c>
       <c r="M11">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -12697,7 +12697,7 @@
         <v>57</v>
       </c>
       <c r="M2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12820,7 +12820,7 @@
         <v>28</v>
       </c>
       <c r="M5">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12940,7 +12940,7 @@
         <v>95</v>
       </c>
       <c r="M8">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13022,7 +13022,7 @@
         <v>248</v>
       </c>
       <c r="M10">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13063,7 +13063,7 @@
         <v>532</v>
       </c>
       <c r="M11">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -13170,7 +13170,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13465,7 +13465,7 @@
         <v>340</v>
       </c>
       <c r="M10">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13506,7 +13506,7 @@
         <v>536</v>
       </c>
       <c r="M11">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -13613,7 +13613,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13938,7 +13938,7 @@
         <v>262</v>
       </c>
       <c r="M10">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13979,7 +13979,7 @@
         <v>526</v>
       </c>
       <c r="M11">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -14275,7 +14275,7 @@
         <v>19</v>
       </c>
       <c r="M8">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14398,7 +14398,7 @@
         <v>99</v>
       </c>
       <c r="M11">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -14581,7 +14581,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14783,7 +14783,7 @@
         <v>25</v>
       </c>
       <c r="M9">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14824,7 +14824,7 @@
         <v>198</v>
       </c>
       <c r="M10">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14865,7 +14865,7 @@
         <v>368</v>
       </c>
       <c r="M11">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -15261,7 +15261,7 @@
         <v>150</v>
       </c>
       <c r="M10">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15302,7 +15302,7 @@
         <v>261</v>
       </c>
       <c r="M11">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -15409,7 +15409,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15491,7 +15491,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15532,7 +15532,7 @@
         <v>33</v>
       </c>
       <c r="M5">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>123</v>
       </c>
       <c r="M8">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15737,7 +15737,7 @@
         <v>281</v>
       </c>
       <c r="M10">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15778,7 +15778,7 @@
         <v>751</v>
       </c>
       <c r="M11">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -16107,7 +16107,7 @@
         <v>64</v>
       </c>
       <c r="M8">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16189,7 +16189,7 @@
         <v>156</v>
       </c>
       <c r="M10">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16230,7 +16230,7 @@
         <v>317</v>
       </c>
       <c r="M11">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -16544,7 +16544,7 @@
         <v>102</v>
       </c>
       <c r="M8">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16585,7 +16585,7 @@
         <v>30</v>
       </c>
       <c r="M9">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16626,7 +16626,7 @@
         <v>697</v>
       </c>
       <c r="M10">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16667,7 +16667,7 @@
         <v>951</v>
       </c>
       <c r="M11">
-        <v>1080</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
@@ -16993,7 +16993,7 @@
         <v>67</v>
       </c>
       <c r="M8">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17075,7 +17075,7 @@
         <v>941</v>
       </c>
       <c r="M10">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17116,7 +17116,7 @@
         <v>1136</v>
       </c>
       <c r="M11">
-        <v>1178</v>
+        <v>1182</v>
       </c>
     </row>
   </sheetData>
@@ -17855,7 +17855,7 @@
         <v>98</v>
       </c>
       <c r="M8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17978,7 +17978,7 @@
         <v>250</v>
       </c>
       <c r="M11">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -19082,7 +19082,7 @@
         <v>50</v>
       </c>
       <c r="M8">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19123,7 +19123,7 @@
         <v>18</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19164,7 +19164,7 @@
         <v>530</v>
       </c>
       <c r="M10">
-        <v>570</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19205,7 +19205,7 @@
         <v>681</v>
       </c>
       <c r="M11">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -19601,7 +19601,7 @@
         <v>447</v>
       </c>
       <c r="M10">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19642,7 +19642,7 @@
         <v>681</v>
       </c>
       <c r="M11">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -19863,7 +19863,7 @@
         <v>30</v>
       </c>
       <c r="M5">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20065,7 +20065,7 @@
         <v>259</v>
       </c>
       <c r="M10">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20106,7 +20106,7 @@
         <v>464</v>
       </c>
       <c r="M11">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -20896,7 +20896,7 @@
         <v>120</v>
       </c>
       <c r="M8">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20937,7 +20937,7 @@
         <v>74</v>
       </c>
       <c r="M9">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -20978,7 +20978,7 @@
         <v>1137</v>
       </c>
       <c r="M10">
-        <v>1070</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21019,7 +21019,7 @@
         <v>1452</v>
       </c>
       <c r="M11">
-        <v>1393</v>
+        <v>1400</v>
       </c>
     </row>
   </sheetData>
@@ -21249,7 +21249,7 @@
         <v>24</v>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21354,7 +21354,7 @@
         <v>79</v>
       </c>
       <c r="M8">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21436,7 +21436,7 @@
         <v>320</v>
       </c>
       <c r="M10">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21477,7 +21477,7 @@
         <v>493</v>
       </c>
       <c r="M11">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -21584,7 +21584,7 @@
         <v>141</v>
       </c>
       <c r="M2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21707,7 +21707,7 @@
         <v>81</v>
       </c>
       <c r="M5">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21830,7 +21830,7 @@
         <v>252</v>
       </c>
       <c r="M8">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21871,7 +21871,7 @@
         <v>115</v>
       </c>
       <c r="M9">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21912,7 +21912,7 @@
         <v>465</v>
       </c>
       <c r="M10">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21953,7 +21953,7 @@
         <v>1252</v>
       </c>
       <c r="M11">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
   </sheetData>
@@ -22352,7 +22352,7 @@
         <v>722</v>
       </c>
       <c r="M10">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22393,7 +22393,7 @@
         <v>1023</v>
       </c>
       <c r="M11">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
   </sheetData>
@@ -22541,7 +22541,7 @@
         <v>70</v>
       </c>
       <c r="M3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22623,7 +22623,7 @@
         <v>73</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22787,7 +22787,7 @@
         <v>73</v>
       </c>
       <c r="M9">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -22828,7 +22828,7 @@
         <v>511</v>
       </c>
       <c r="M10">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22869,7 +22869,7 @@
         <v>968</v>
       </c>
       <c r="M11">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>
@@ -23066,7 +23066,7 @@
         <v>25</v>
       </c>
       <c r="M5">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23142,7 +23142,7 @@
         <v>30</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -23224,7 +23224,7 @@
         <v>129</v>
       </c>
       <c r="M9">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23265,7 +23265,7 @@
         <v>205</v>
       </c>
       <c r="M10">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -23691,7 +23691,7 @@
         <v>222</v>
       </c>
       <c r="M10">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23732,7 +23732,7 @@
         <v>370</v>
       </c>
       <c r="M11">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -23839,7 +23839,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23962,7 +23962,7 @@
         <v>47</v>
       </c>
       <c r="M5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24085,7 +24085,7 @@
         <v>156</v>
       </c>
       <c r="M8">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24126,7 +24126,7 @@
         <v>77</v>
       </c>
       <c r="M9">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -24167,7 +24167,7 @@
         <v>462</v>
       </c>
       <c r="M10">
-        <v>606</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24208,7 +24208,7 @@
         <v>935</v>
       </c>
       <c r="M11">
-        <v>1148</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -24737,7 +24737,7 @@
         <v>82</v>
       </c>
       <c r="M2">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24860,7 +24860,7 @@
         <v>66</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24983,7 +24983,7 @@
         <v>219</v>
       </c>
       <c r="M8">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25024,7 +25024,7 @@
         <v>75</v>
       </c>
       <c r="M9">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -25065,7 +25065,7 @@
         <v>362</v>
       </c>
       <c r="M10">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25106,7 +25106,7 @@
         <v>923</v>
       </c>
       <c r="M11">
-        <v>814</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -25517,7 +25517,7 @@
         <v>104</v>
       </c>
       <c r="M10">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25558,7 +25558,7 @@
         <v>282</v>
       </c>
       <c r="M11">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -25881,7 +25881,7 @@
         <v>28</v>
       </c>
       <c r="M8">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26004,7 +26004,7 @@
         <v>141</v>
       </c>
       <c r="M11">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -26111,7 +26111,7 @@
         <v>49</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26152,7 +26152,7 @@
         <v>27</v>
       </c>
       <c r="M3">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26342,7 +26342,7 @@
         <v>150</v>
       </c>
       <c r="M8">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26383,7 +26383,7 @@
         <v>25</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -26424,7 +26424,7 @@
         <v>217</v>
       </c>
       <c r="M10">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26465,7 +26465,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -27183,7 +27183,7 @@
         <v>50</v>
       </c>
       <c r="M8">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27265,7 +27265,7 @@
         <v>302</v>
       </c>
       <c r="M10">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27306,7 +27306,7 @@
         <v>428</v>
       </c>
       <c r="M11">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -27678,7 +27678,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27719,7 +27719,7 @@
         <v>314</v>
       </c>
       <c r="M11">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -27867,7 +27867,7 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27937,7 +27937,7 @@
         <v>39</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28136,7 +28136,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28177,7 +28177,7 @@
         <v>634</v>
       </c>
       <c r="M11">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -28558,7 +28558,7 @@
         <v>148</v>
       </c>
       <c r="M10">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28599,7 +28599,7 @@
         <v>219</v>
       </c>
       <c r="M11">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -28986,7 +28986,7 @@
         <v>118</v>
       </c>
       <c r="M10">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29027,7 +29027,7 @@
         <v>191</v>
       </c>
       <c r="M11">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -29213,7 +29213,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -29453,7 +29453,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29494,7 +29494,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -29721,7 +29721,7 @@
         <v>38</v>
       </c>
       <c r="M5">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29838,7 +29838,7 @@
         <v>83</v>
       </c>
       <c r="M8">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29920,7 +29920,7 @@
         <v>414</v>
       </c>
       <c r="M10">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29961,7 +29961,7 @@
         <v>678</v>
       </c>
       <c r="M11">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -30167,7 +30167,7 @@
         <v>14</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30328,7 +30328,7 @@
         <v>16</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -30369,7 +30369,7 @@
         <v>253</v>
       </c>
       <c r="M10">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>463</v>
       </c>
       <c r="M11">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -30754,7 +30754,7 @@
         <v>97</v>
       </c>
       <c r="M8">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30877,7 +30877,7 @@
         <v>371</v>
       </c>
       <c r="M11">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -31203,7 +31203,7 @@
         <v>123</v>
       </c>
       <c r="M8">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31285,7 +31285,7 @@
         <v>325</v>
       </c>
       <c r="M10">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31326,7 +31326,7 @@
         <v>563</v>
       </c>
       <c r="M11">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -31556,7 +31556,7 @@
         <v>59</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31720,7 +31720,7 @@
         <v>59</v>
       </c>
       <c r="M9">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -31761,7 +31761,7 @@
         <v>334</v>
       </c>
       <c r="M10">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31802,7 +31802,7 @@
         <v>710</v>
       </c>
       <c r="M11">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -32599,7 +32599,7 @@
         <v>202</v>
       </c>
       <c r="M10">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32640,7 +32640,7 @@
         <v>352</v>
       </c>
       <c r="M11">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -32747,7 +32747,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -32984,7 +32984,7 @@
         <v>101</v>
       </c>
       <c r="M8">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33025,7 +33025,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -33066,7 +33066,7 @@
         <v>182</v>
       </c>
       <c r="M10">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33107,7 +33107,7 @@
         <v>393</v>
       </c>
       <c r="M11">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -33509,7 +33509,7 @@
         <v>275</v>
       </c>
       <c r="M10">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33550,7 +33550,7 @@
         <v>384</v>
       </c>
       <c r="M11">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -33765,7 +33765,7 @@
         <v>22</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -33908,7 +33908,7 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -33949,7 +33949,7 @@
         <v>205</v>
       </c>
       <c r="M10">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33990,7 +33990,7 @@
         <v>330</v>
       </c>
       <c r="M11">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -34398,7 +34398,7 @@
         <v>101</v>
       </c>
       <c r="M10">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34439,7 +34439,7 @@
         <v>256</v>
       </c>
       <c r="M11">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -34546,7 +34546,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -34720,7 +34720,7 @@
         <v>31</v>
       </c>
       <c r="M8">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -34799,7 +34799,7 @@
         <v>221</v>
       </c>
       <c r="M10">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34840,7 +34840,7 @@
         <v>276</v>
       </c>
       <c r="M11">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -35602,7 +35602,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -35643,7 +35643,7 @@
         <v>195</v>
       </c>
       <c r="M10">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -35791,7 +35791,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -36050,7 +36050,7 @@
         <v>106</v>
       </c>
       <c r="M11">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -36157,7 +36157,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -36464,7 +36464,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36505,7 +36505,7 @@
         <v>350</v>
       </c>
       <c r="M11">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -36883,7 +36883,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36924,7 +36924,7 @@
         <v>265</v>
       </c>
       <c r="M11">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -37305,7 +37305,7 @@
         <v>444</v>
       </c>
       <c r="M10">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37346,7 +37346,7 @@
         <v>596</v>
       </c>
       <c r="M11">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -37916,7 +37916,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -38161,7 +38161,7 @@
         <v>159</v>
       </c>
       <c r="M10">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38202,7 +38202,7 @@
         <v>241</v>
       </c>
       <c r="M11">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -38560,7 +38560,7 @@
         <v>149</v>
       </c>
       <c r="M9">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -38601,7 +38601,7 @@
         <v>187</v>
       </c>
       <c r="M10">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -39018,7 +39018,7 @@
         <v>136</v>
       </c>
       <c r="M10">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39059,7 +39059,7 @@
         <v>258</v>
       </c>
       <c r="M11">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -39207,7 +39207,7 @@
         <v>26</v>
       </c>
       <c r="M3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -39286,7 +39286,7 @@
         <v>56</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -39476,7 +39476,7 @@
         <v>518</v>
       </c>
       <c r="M10">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39517,7 +39517,7 @@
         <v>735</v>
       </c>
       <c r="M11">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -40945,7 +40945,7 @@
         <v>25</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40986,7 +40986,7 @@
         <v>30</v>
       </c>
       <c r="M11">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -41361,7 +41361,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41402,7 +41402,7 @@
         <v>438</v>
       </c>
       <c r="M11">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -41573,7 +41573,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -41719,7 +41719,7 @@
         <v>51</v>
       </c>
       <c r="M8">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41760,7 +41760,7 @@
         <v>82</v>
       </c>
       <c r="M9">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -42930,7 +42930,7 @@
         <v>63</v>
       </c>
       <c r="M10">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42971,7 +42971,7 @@
         <v>103</v>
       </c>
       <c r="M11">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -43577,7 +43577,7 @@
         <v>173</v>
       </c>
       <c r="M3">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43618,7 +43618,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -43659,7 +43659,7 @@
         <v>106</v>
       </c>
       <c r="M5">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43782,7 +43782,7 @@
         <v>232</v>
       </c>
       <c r="M8">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43864,7 +43864,7 @@
         <v>552</v>
       </c>
       <c r="M10">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43905,7 +43905,7 @@
         <v>1325</v>
       </c>
       <c r="M11">
-        <v>1289</v>
+        <v>1299</v>
       </c>
     </row>
   </sheetData>
@@ -44213,7 +44213,7 @@
         <v>13</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44336,7 +44336,7 @@
         <v>99</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -44638,7 +44638,7 @@
         <v>56</v>
       </c>
       <c r="M8">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44679,7 +44679,7 @@
         <v>67</v>
       </c>
       <c r="M9">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -45457,7 +45457,7 @@
         <v>49</v>
       </c>
       <c r="M8">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45539,7 +45539,7 @@
         <v>154</v>
       </c>
       <c r="M10">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45580,7 +45580,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -45908,7 +45908,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45949,7 +45949,7 @@
         <v>139</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -46502,7 +46502,7 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46565,7 +46565,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46676,7 +46676,7 @@
         <v>67</v>
       </c>
       <c r="M11">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -47281,7 +47281,7 @@
         <v>26</v>
       </c>
       <c r="M8">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47322,7 +47322,7 @@
         <v>4</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47363,7 +47363,7 @@
         <v>92</v>
       </c>
       <c r="M10">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47404,7 +47404,7 @@
         <v>151</v>
       </c>
       <c r="M11">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -47704,7 +47704,7 @@
         <v>27</v>
       </c>
       <c r="M10">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47745,7 +47745,7 @@
         <v>43</v>
       </c>
       <c r="M11">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
